--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6405.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6405.xlsx
@@ -3968,6 +3968,9 @@
       <c r="G49" t="n">
         <v>0.125</v>
       </c>
+      <c r="I49" t="n">
+        <v>1.72</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>6405-16-24-O</t>
@@ -3980,12 +3983,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: HEXB@HEX, L31@DRIVE, ORB_GRVDIA@DRIVE, ORB_GRVW@DRIVE, THDMAJ_A@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE_A] [BRENNAN-CAD 2026-10-21: HEXB@HEX, L31@DRIVE, ORB_GRVDIA@DRIVE, ORB_GRVW@DRIVE, THDMAJ_A@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 6405-16-24-O (PARTcommunity / CADENAS, HEXB@HEX=C4, L31@DRIVE=L, ORB_GRVDIA@DRIVE=CL, ORB_GRVW@DRIVE=DL, THDMAJ_A@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 6405-16-24-O (PARTcommunity / CADENAS, HEXB@HEX=C4, L31@DRIVE=L, ORB_GRVDIA@DRIVE=CL, ORB_GRVW@DRIVE=DL, THDMAJ_A@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE_A = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4022,6 +4025,9 @@
       <c r="F50" t="n">
         <v>2.381</v>
       </c>
+      <c r="I50" t="n">
+        <v>1.14</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>6405-32-16-O</t>
@@ -4034,12 +4040,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: HEXB@HEX, L31@DRIVE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE_A] [BRENNAN-CAD 2026-10-21: HEXB@HEX, L31@DRIVE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 6405-32-16-O (PARTcommunity / CADENAS, HEXB@HEX=C4, L31@DRIVE=L, ORB_GRVDIA@DRIVE=CL, THDMAJ_A@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 6405-32-16-O (PARTcommunity / CADENAS, HEXB@HEX=C4, L31@DRIVE=L, ORB_GRVDIA@DRIVE=CL, THDMAJ_A@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE_A = Air-Way per-size tap drill -16 1.14 (A1)</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
